--- a/data/outputs/Data_Figure_5.xlsx
+++ b/data/outputs/Data_Figure_5.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\01_3rd_submission\Manuscript_datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\02_Final_revision\0_Final_submission\Manuscript_datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8AFA5A-5C9A-4669-9AC9-CD38F3D90B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32362511-0A99-4FB3-A660-3FD6C8E2B6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="2175" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fig 5" sheetId="1" r:id="rId1"/>
-    <sheet name="Data FHN" sheetId="2" r:id="rId2"/>
-    <sheet name="Data GDP" sheetId="3" r:id="rId3"/>
+    <sheet name="Figure 5" sheetId="1" r:id="rId1"/>
+    <sheet name="Data ethics-based allocation" sheetId="2" r:id="rId2"/>
+    <sheet name="Data economic-based allocation" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -56,18 +56,6 @@
     <t>Desciption</t>
   </si>
   <si>
-    <t>Maximal annual trafic growth (2023-2050) to respect share of SOS under FHN</t>
-  </si>
-  <si>
-    <t>Data FHN</t>
-  </si>
-  <si>
-    <t>Data GDP</t>
-  </si>
-  <si>
-    <t>Maximal annual trafic growth (2023-2050) to respect share of SOS under GDP</t>
-  </si>
-  <si>
     <t>Already transgressed</t>
   </si>
   <si>
@@ -102,6 +90,18 @@
   </si>
   <si>
     <t>Efuel-RES</t>
+  </si>
+  <si>
+    <t>Data ethics-based allocation</t>
+  </si>
+  <si>
+    <t>Data economic-based allocation</t>
+  </si>
+  <si>
+    <t>Maximal annual trafic growth (2023-2050) to respect share of SOS under ethics-based allocation</t>
+  </si>
+  <si>
+    <t>Maximal annual trafic growth (2023-2050) to respect share of SOS under economic-based allocation</t>
   </si>
 </sst>
 </file>
@@ -1036,18 +1036,18 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1096,13 +1096,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" s="11">
         <v>-2.9000000000000001E-2</v>
@@ -1111,24 +1111,24 @@
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" s="13">
         <v>-0.09</v>
@@ -1137,114 +1137,114 @@
         <v>-7.1999999999999995E-2</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5" s="13">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E6" s="13">
         <v>-9.6000000000000002E-2</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H7" s="14">
         <v>8.5999999999999993E-2</v>
@@ -1252,25 +1252,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" s="14">
         <v>6.6000000000000003E-2</v>
@@ -1278,54 +1278,54 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E9" s="13">
         <v>-0.08</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9" s="13">
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" s="17">
         <v>-9.1999999999999998E-2</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1375,62 +1375,62 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" s="13">
         <v>-8.9999999999999993E-3</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4" s="13">
         <v>-2.3E-2</v>
@@ -1439,24 +1439,24 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5" s="13">
         <v>-1.52E-2</v>
@@ -1465,24 +1465,24 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5" s="13">
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" s="13">
         <v>-1.52E-2</v>
@@ -1491,24 +1491,24 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="13">
         <v>-2.93E-2</v>
@@ -1517,24 +1517,24 @@
         <v>6.2E-2</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" s="13">
         <v>-3.0000000000000001E-3</v>
@@ -1543,24 +1543,24 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" s="13">
         <v>-7.0000000000000001E-3</v>
@@ -1569,24 +1569,24 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9" s="13">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10" s="17">
         <v>7.0000000000000001E-3</v>
@@ -1595,16 +1595,16 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
